--- a/Antithetic_Results_Rule2.xlsx
+++ b/Antithetic_Results_Rule2.xlsx
@@ -444,13 +444,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>23.23453235057933</v>
+        <v>75.23125216923722</v>
       </c>
       <c r="C2" t="n">
-        <v>2.856710304055404</v>
+        <v>2.040069801139098</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4557130438072234</v>
+        <v>0.6744794947847245</v>
       </c>
     </row>
   </sheetData>
@@ -494,13 +494,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>25.45738046766895</v>
+        <v>27.46349948579652</v>
       </c>
       <c r="C2" t="n">
-        <v>2.860622654048847</v>
+        <v>2.043038711107193</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4693789881542506</v>
+        <v>0.3904775124591118</v>
       </c>
     </row>
   </sheetData>
